--- a/docs/FEATURE_STORY_TEST_TRACKER.xlsx
+++ b/docs/FEATURE_STORY_TEST_TRACKER.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
